--- a/docs/ValueSet-ahip-religion-jewish-detail.xlsx
+++ b/docs/ValueSet-ahip-religion-jewish-detail.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AHIP Jewish Religion Detail Codes</t>
+    <t>Used as the answer options for the Jewish movement detail question, shown only when the patient selects Judaism on the religion/spirituality question.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -126,7 +126,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-ahip-religion-jewish-detail.xlsx
+++ b/docs/ValueSet-ahip-religion-jewish-detail.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -126,7 +126,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
   </si>
 </sst>
 </file>
